--- a/event_financial_reports/2026/02_February/02-23-2026_weekly_report/02-23-2026_weekly_report.xlsx
+++ b/event_financial_reports/2026/02_February/02-23-2026_weekly_report/02-23-2026_weekly_report.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidcuvin/purveyor_project/event_financial_reports/2026/02_February/02-23-2026_weekly_report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FADD1B71-8BB4-9447-B183-1A0D1F2CB8BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70858F42-0E4F-6D48-8C15-43903A91284B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33540" yWindow="180" windowWidth="27800" windowHeight="17480" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="880" yWindow="1280" windowWidth="27800" windowHeight="17480" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Event_PnL" sheetId="5" r:id="rId1"/>
-    <sheet name="Labor" sheetId="3" r:id="rId2"/>
-    <sheet name="Invoices" sheetId="4" r:id="rId3"/>
-    <sheet name="Weekly Summary" sheetId="6" r:id="rId4"/>
-    <sheet name="Charts" sheetId="8" r:id="rId5"/>
+    <sheet name="Weekly Info" sheetId="10" r:id="rId1"/>
+    <sheet name="Event_PnL" sheetId="9" r:id="rId2"/>
+    <sheet name="Weekly Summary" sheetId="6" r:id="rId3"/>
+    <sheet name="Labor" sheetId="3" r:id="rId4"/>
+    <sheet name="Invoices" sheetId="4" r:id="rId5"/>
+    <sheet name="Charts" sheetId="8" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
     <author>David Cuvin</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{7A54C134-34F4-C144-961D-1154B6ECA0E7}">
+    <comment ref="C18" authorId="0" shapeId="0" xr:uid="{D1652067-3673-6245-AC97-60B3C5FA5074}">
       <text>
         <r>
           <rPr>
@@ -71,12 +72,12 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">costs of any addiotonal labor and/ outsourced labor
+          <t xml:space="preserve">Had to manually tally certain items from several invoices
 </t>
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{48431B31-3A47-E747-8C7D-E49BB71821BA}">
+    <comment ref="A19" authorId="0" shapeId="0" xr:uid="{DF7890CD-0BEE-494A-A9E8-17B330A2D8AA}">
       <text>
         <r>
           <rPr>
@@ -105,12 +106,22 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">cost of BOH and FOH Event Staff
+          <t xml:space="preserve">Currently unknow, so defaulting to 22% of Beverage Revenue
 </t>
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{75E4C65D-6571-1245-A827-C6486842A989}">
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>David Cuvin</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{EB595F93-B3E2-1F45-A1C0-5B130F428130}">
       <text>
         <r>
           <rPr>
@@ -139,240 +150,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">cost of renting evnet spaces
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{81684773-129F-2C4D-9A75-DDE8E35582A6}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>David Cuvin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>cost of bev package</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{09C3215F-7397-C14C-AF4B-FCA40F95A564}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>David Cuvin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>cost of food package</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{4EBF9698-1589-EF49-8702-B6AF39F6C65F}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>David Cuvin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>total cost of entire event</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{1D142310-C96E-B94C-8FE8-D14B5A4FC132}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>David Cuvin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">food + Bev + Space Fee + admin fee </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="O1" authorId="0" shapeId="0" xr:uid="{F0A16B0B-331A-B940-8021-7977857F6991}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>David Cuvin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Revenue - Food Cost - Labor Cost</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="P1" authorId="0" shapeId="0" xr:uid="{BB85A4C0-C142-3942-AAB3-DFD4BD135472}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>David Cuvin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>margin% = (operating_profit/ revenue) x 100</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B2" authorId="0" shapeId="0" xr:uid="{C73637A4-D395-9E48-9C1F-1C6823F403F0}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>David Cuvin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">20% discount applied
-</t>
+          <t>Total revenue before costs</t>
         </r>
       </text>
     </comment>
@@ -380,7 +158,7 @@
 </comments>
 </file>
 
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>David Cuvin</author>
@@ -491,51 +269,8 @@
 </comments>
 </file>
 
-<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>David Cuvin</author>
-  </authors>
-  <commentList>
-    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{EB595F93-B3E2-1F45-A1C0-5B130F428130}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>David Cuvin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Total revenue before costs</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="77">
   <si>
     <t>notes</t>
   </si>
@@ -552,9 +287,6 @@
     <t>guest_count</t>
   </si>
   <si>
-    <t>revenue</t>
-  </si>
-  <si>
     <t>invoice_date</t>
   </si>
   <si>
@@ -570,18 +302,12 @@
     <t>total_cost</t>
   </si>
   <si>
-    <t>allocated_food_cost</t>
-  </si>
-  <si>
     <t>margin_pct</t>
   </si>
   <si>
     <t>revenue_per_guest</t>
   </si>
   <si>
-    <t>food_cost_per_guest</t>
-  </si>
-  <si>
     <t>labor_cost_per_guest</t>
   </si>
   <si>
@@ -591,9 +317,6 @@
     <t>value</t>
   </si>
   <si>
-    <t>Total Food Cost</t>
-  </si>
-  <si>
     <t>Total Labor Cost</t>
   </si>
   <si>
@@ -606,12 +329,6 @@
     <t>space_fee</t>
   </si>
   <si>
-    <t>grand_total</t>
-  </si>
-  <si>
-    <t>allocated_bev_cost</t>
-  </si>
-  <si>
     <t>admin_fee</t>
   </si>
   <si>
@@ -633,9 +350,6 @@
     <t>Ruba Katrib</t>
   </si>
   <si>
-    <t>Birthday / Cheese &amp; Charcuterie</t>
-  </si>
-  <si>
     <t>event_labor_cost</t>
   </si>
   <si>
@@ -702,9 +416,6 @@
     <t>Opertaing Cost</t>
   </si>
   <si>
-    <t xml:space="preserve">Operating Profit </t>
-  </si>
-  <si>
     <t>Profit Margin %</t>
   </si>
   <si>
@@ -714,9 +425,6 @@
     <t>Operating Cost %</t>
   </si>
   <si>
-    <t>Operating Profit  %</t>
-  </si>
-  <si>
     <t>Liepper</t>
   </si>
   <si>
@@ -724,9 +432,6 @@
   </si>
   <si>
     <t>9 x sides hamachi</t>
-  </si>
-  <si>
-    <t>Total Food Cost %</t>
   </si>
   <si>
     <t>Total Labor Cost %</t>
@@ -747,6 +452,66 @@
       </rPr>
       <t>TCW7400278862</t>
     </r>
+  </si>
+  <si>
+    <t>net_revenue</t>
+  </si>
+  <si>
+    <t>gross_revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Operating Profit </t>
+  </si>
+  <si>
+    <t>food_revenue</t>
+  </si>
+  <si>
+    <t>beverage_revenue</t>
+  </si>
+  <si>
+    <t>outsourced_labor_cost</t>
+  </si>
+  <si>
+    <t>profit_per_guest</t>
+  </si>
+  <si>
+    <t>approx_operating_cost</t>
+  </si>
+  <si>
+    <t>week_start</t>
+  </si>
+  <si>
+    <t>week_end</t>
+  </si>
+  <si>
+    <t>total_guests</t>
+  </si>
+  <si>
+    <t>number_of_paid_events</t>
+  </si>
+  <si>
+    <t>carrots, squash</t>
+  </si>
+  <si>
+    <t>Total Food and Bev Cost</t>
+  </si>
+  <si>
+    <t>Total Food and Bev Cost %</t>
+  </si>
+  <si>
+    <t>total_labor_cost</t>
+  </si>
+  <si>
+    <t>food_and_bev_cost_per_guest</t>
+  </si>
+  <si>
+    <t>approx_food_cost</t>
+  </si>
+  <si>
+    <t>approx_beverage_cost</t>
+  </si>
+  <si>
+    <t>Birthday/ Cheese &amp; Charcuterie</t>
   </si>
 </sst>
 </file>
@@ -763,12 +528,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -795,6 +554,14 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="16"/>
@@ -854,7 +621,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -867,8 +634,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -876,57 +655,102 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="10" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -947,24 +771,6 @@
     </xf>
     <xf numFmtId="168" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="13" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="10" fontId="13" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="168" fontId="13" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -993,6 +799,97 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1294,214 +1191,715 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:S3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="21" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38BE7C21-6CE1-F34C-BE72-4C2E7F9DF544}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.1640625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="49" style="3" customWidth="1"/>
-    <col min="3" max="5" width="47.1640625" style="3" customWidth="1"/>
-    <col min="6" max="7" width="47.1640625" style="7" customWidth="1"/>
-    <col min="8" max="8" width="26.5" style="7" customWidth="1"/>
-    <col min="9" max="9" width="23" style="7" customWidth="1"/>
-    <col min="10" max="10" width="19.33203125" style="7" customWidth="1"/>
-    <col min="11" max="11" width="16.83203125" style="7" customWidth="1"/>
-    <col min="12" max="12" width="14" style="7" customWidth="1"/>
-    <col min="13" max="15" width="16" style="7" customWidth="1"/>
-    <col min="16" max="16" width="19.33203125" style="8" customWidth="1"/>
-    <col min="17" max="17" width="21" style="9" customWidth="1"/>
-    <col min="18" max="18" width="23" style="9" customWidth="1"/>
-    <col min="19" max="19" width="24" style="9" customWidth="1"/>
-    <col min="20" max="16384" width="8.83203125" style="3"/>
+    <col min="1" max="1" width="44.5" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="31" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+    <row r="1" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+      <c r="A1" s="46" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="59">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+      <c r="A2" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="B2" s="59">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+      <c r="A3" s="32" t="s">
+        <v>68</v>
+      </c>
+      <c r="B3" s="60">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="21" x14ac:dyDescent="0.25">
+      <c r="A4" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" s="60">
+        <v>150</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB9E1A0F-2579-C14E-AA5C-FB621DFBD8C3}">
+  <dimension ref="A1:J30"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="21" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="35.83203125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="38.6640625" style="45" customWidth="1"/>
+    <col min="3" max="3" width="36.1640625" style="45" customWidth="1"/>
+    <col min="4" max="4" width="30.5" style="45" customWidth="1"/>
+    <col min="5" max="10" width="10.83203125" style="45"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="33" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="39">
+        <v>46081</v>
+      </c>
+      <c r="C1" s="39">
+        <v>46082</v>
+      </c>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+    </row>
+    <row r="2" spans="1:10" s="34" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="B2" s="40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+    </row>
+    <row r="3" spans="1:10" s="34" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="B3" s="40" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="40" t="s">
+        <v>76</v>
+      </c>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+    </row>
+    <row r="4" spans="1:10" s="36" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="G1" s="28" t="s">
+      <c r="B4" s="41">
+        <v>133</v>
+      </c>
+      <c r="C4" s="41">
         <v>30</v>
       </c>
-      <c r="H1" s="28" t="s">
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="41"/>
+      <c r="J4" s="41"/>
+    </row>
+    <row r="5" spans="1:10" s="38" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="37"/>
+      <c r="B5" s="42"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="42"/>
+    </row>
+    <row r="6" spans="1:10" s="50" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="47" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="48">
+        <v>10000</v>
+      </c>
+      <c r="C6" s="48">
+        <v>0</v>
+      </c>
+      <c r="D6" s="49"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="49"/>
+      <c r="I6" s="49"/>
+      <c r="J6" s="49"/>
+    </row>
+    <row r="7" spans="1:10" s="52" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" s="48">
+        <v>29967</v>
+      </c>
+      <c r="C7" s="48">
+        <v>700</v>
+      </c>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="48"/>
+    </row>
+    <row r="8" spans="1:10" s="52" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8" s="48">
+        <v>16320</v>
+      </c>
+      <c r="C8" s="48">
+        <v>2475</v>
+      </c>
+      <c r="D8" s="48"/>
+      <c r="E8" s="48"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="48"/>
+      <c r="H8" s="48"/>
+      <c r="I8" s="48"/>
+      <c r="J8" s="48"/>
+    </row>
+    <row r="9" spans="1:10" s="52" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="51" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="48">
+        <v>13072.51</v>
+      </c>
+      <c r="C9" s="48">
+        <v>730.25</v>
+      </c>
+      <c r="D9" s="48"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="48"/>
+      <c r="H9" s="48"/>
+      <c r="I9" s="48"/>
+      <c r="J9" s="48"/>
+    </row>
+    <row r="10" spans="1:10" s="52" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="51" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="53">
+        <v>6204.47</v>
+      </c>
+      <c r="C10" s="53">
+        <v>346.59</v>
+      </c>
+      <c r="D10" s="48"/>
+      <c r="E10" s="48"/>
+      <c r="F10" s="48"/>
+      <c r="G10" s="48"/>
+      <c r="H10" s="48"/>
+      <c r="I10" s="48"/>
+      <c r="J10" s="48"/>
+    </row>
+    <row r="11" spans="1:10" s="52" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" s="62">
+        <v>76113.98</v>
+      </c>
+      <c r="C11" s="54">
+        <v>4251.84</v>
+      </c>
+      <c r="D11" s="48"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="48"/>
+      <c r="G11" s="48"/>
+      <c r="H11" s="48"/>
+      <c r="I11" s="48"/>
+      <c r="J11" s="48"/>
+    </row>
+    <row r="12" spans="1:10" s="56" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="55" t="s">
+        <v>57</v>
+      </c>
+      <c r="B12" s="49">
+        <f>B11-B10</f>
+        <v>69909.509999999995</v>
+      </c>
+      <c r="C12" s="49">
+        <f>C11-C10</f>
+        <v>3905.25</v>
+      </c>
+      <c r="D12" s="53"/>
+      <c r="E12" s="53"/>
+      <c r="F12" s="53"/>
+      <c r="G12" s="53"/>
+      <c r="H12" s="53"/>
+      <c r="I12" s="53"/>
+      <c r="J12" s="53"/>
+    </row>
+    <row r="13" spans="1:10" s="38" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="37"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="42"/>
+    </row>
+    <row r="14" spans="1:10" s="52" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="57" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="58">
+        <v>550</v>
+      </c>
+      <c r="C14" s="58">
+        <v>0</v>
+      </c>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="H14" s="48"/>
+      <c r="I14" s="48"/>
+      <c r="J14" s="48"/>
+    </row>
+    <row r="15" spans="1:10" s="52" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="28" t="s">
+      <c r="B15" s="49">
+        <v>7572.1</v>
+      </c>
+      <c r="C15" s="49">
+        <v>1269.7</v>
+      </c>
+      <c r="D15" s="48"/>
+      <c r="E15" s="48"/>
+      <c r="F15" s="48"/>
+      <c r="G15" s="48"/>
+      <c r="H15" s="48"/>
+      <c r="I15" s="48"/>
+      <c r="J15" s="48"/>
+    </row>
+    <row r="16" spans="1:10" s="52" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B16" s="48">
+        <v>0</v>
+      </c>
+      <c r="C16" s="48">
+        <v>0</v>
+      </c>
+      <c r="D16" s="48"/>
+      <c r="E16" s="48"/>
+      <c r="F16" s="48"/>
+      <c r="G16" s="48"/>
+      <c r="H16" s="48"/>
+      <c r="I16" s="48"/>
+      <c r="J16" s="48"/>
+    </row>
+    <row r="17" spans="1:10" s="52" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="B17" s="49">
+        <f>SUM(B14:B16)</f>
+        <v>8122.1</v>
+      </c>
+      <c r="C17" s="49">
+        <f>SUM(C14:C16)</f>
+        <v>1269.7</v>
+      </c>
+      <c r="D17" s="48"/>
+      <c r="E17" s="48"/>
+      <c r="F17" s="48"/>
+      <c r="G17" s="48"/>
+      <c r="H17" s="48"/>
+      <c r="I17" s="48"/>
+      <c r="J17" s="48"/>
+    </row>
+    <row r="18" spans="1:10" s="52" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="B18" s="49">
+        <f>Invoices!G2</f>
+        <v>6311.9999999999991</v>
+      </c>
+      <c r="C18" s="49">
+        <v>654.35</v>
+      </c>
+      <c r="D18" s="48"/>
+      <c r="E18" s="48"/>
+      <c r="F18" s="48"/>
+      <c r="G18" s="48"/>
+      <c r="H18" s="48"/>
+      <c r="I18" s="48"/>
+      <c r="J18" s="48"/>
+    </row>
+    <row r="19" spans="1:10" s="52" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19" s="49">
+        <f xml:space="preserve"> 20% * B8</f>
+        <v>3264</v>
+      </c>
+      <c r="C19" s="49">
+        <f xml:space="preserve"> 20% * C8</f>
+        <v>495</v>
+      </c>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="48"/>
+      <c r="H19" s="48"/>
+      <c r="I19" s="48"/>
+      <c r="J19" s="48"/>
+    </row>
+    <row r="20" spans="1:10" s="52" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="J1" s="28" t="s">
+      <c r="B20" s="48">
+        <v>0</v>
+      </c>
+      <c r="C20" s="48">
+        <v>0</v>
+      </c>
+      <c r="D20" s="48"/>
+      <c r="E20" s="48"/>
+      <c r="F20" s="48"/>
+      <c r="G20" s="48"/>
+      <c r="H20" s="48"/>
+      <c r="I20" s="48"/>
+      <c r="J20" s="48"/>
+    </row>
+    <row r="21" spans="1:10" s="56" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="55" t="s">
+        <v>64</v>
+      </c>
+      <c r="B21" s="53">
+        <f xml:space="preserve"> SUM(B14:B20)</f>
+        <v>25820.2</v>
+      </c>
+      <c r="C21" s="53">
+        <f xml:space="preserve"> SUM(C14:C20)</f>
+        <v>3688.75</v>
+      </c>
+      <c r="D21" s="53"/>
+      <c r="E21" s="53"/>
+      <c r="F21" s="53"/>
+      <c r="G21" s="53"/>
+      <c r="H21" s="53"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="53"/>
+    </row>
+    <row r="22" spans="1:10" s="38" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="37"/>
+      <c r="B22" s="42"/>
+      <c r="C22" s="42"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="42"/>
+      <c r="F22" s="42"/>
+      <c r="G22" s="42"/>
+      <c r="H22" s="42"/>
+      <c r="I22" s="42"/>
+      <c r="J22" s="42"/>
+    </row>
+    <row r="23" spans="1:10" s="50" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="49">
+        <f>B12-B21</f>
+        <v>44089.31</v>
+      </c>
+      <c r="C23" s="49">
+        <f>C12-C21</f>
+        <v>216.5</v>
+      </c>
+      <c r="D23" s="49"/>
+      <c r="E23" s="49"/>
+      <c r="F23" s="49"/>
+      <c r="G23" s="49"/>
+      <c r="H23" s="49"/>
+      <c r="I23" s="49"/>
+      <c r="J23" s="49"/>
+    </row>
+    <row r="24" spans="1:10" s="36" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="35" t="s">
+        <v>10</v>
+      </c>
+      <c r="B24" s="43">
+        <f>B23/B12</f>
+        <v>0.63066255220498613</v>
+      </c>
+      <c r="C24" s="43">
+        <f>C23/C12</f>
+        <v>5.5438192177197365E-2</v>
+      </c>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="41"/>
+      <c r="H24" s="41"/>
+      <c r="I24" s="41"/>
+      <c r="J24" s="41"/>
+    </row>
+    <row r="25" spans="1:10" s="38" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="37"/>
+      <c r="B25" s="42"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="42"/>
+      <c r="H25" s="42"/>
+      <c r="I25" s="42"/>
+      <c r="J25" s="42"/>
+    </row>
+    <row r="26" spans="1:10" s="50" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="K1" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="L1" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="M1" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="N1" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="O1" s="28" t="s">
-        <v>29</v>
-      </c>
-      <c r="P1" s="29" t="s">
+      <c r="B26" s="48">
+        <f>B12/B4</f>
+        <v>525.63541353383459</v>
+      </c>
+      <c r="C26" s="48">
+        <f>C12/C4</f>
+        <v>130.17500000000001</v>
+      </c>
+      <c r="D26" s="49"/>
+      <c r="E26" s="49"/>
+      <c r="F26" s="49"/>
+      <c r="G26" s="49"/>
+      <c r="H26" s="49"/>
+      <c r="I26" s="49"/>
+      <c r="J26" s="49"/>
+    </row>
+    <row r="27" spans="1:10" s="52" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="51" t="s">
+        <v>73</v>
+      </c>
+      <c r="B27" s="48">
+        <f>(B18 + B19) / B4</f>
+        <v>72</v>
+      </c>
+      <c r="C27" s="48">
+        <f>(C18 + C19) / C4</f>
+        <v>38.31166666666666</v>
+      </c>
+      <c r="D27" s="48"/>
+      <c r="E27" s="48"/>
+      <c r="F27" s="48"/>
+      <c r="G27" s="48"/>
+      <c r="H27" s="48"/>
+      <c r="I27" s="48"/>
+      <c r="J27" s="48"/>
+    </row>
+    <row r="28" spans="1:10" s="52" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="Q1" s="30" t="s">
+      <c r="B28" s="53">
+        <f xml:space="preserve"> SUM(B14:B16) / B4</f>
+        <v>61.068421052631585</v>
+      </c>
+      <c r="C28" s="53">
+        <f xml:space="preserve"> SUM(C14:C16) / C4</f>
+        <v>42.323333333333338</v>
+      </c>
+      <c r="D28" s="48"/>
+      <c r="E28" s="48"/>
+      <c r="F28" s="48"/>
+      <c r="G28" s="48"/>
+      <c r="H28" s="48"/>
+      <c r="I28" s="48"/>
+      <c r="J28" s="48"/>
+    </row>
+    <row r="29" spans="1:10" s="56" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="55" t="s">
+        <v>63</v>
+      </c>
+      <c r="B29" s="53">
+        <f>B26-B27-B28</f>
+        <v>392.56699248120299</v>
+      </c>
+      <c r="C29" s="53">
+        <f>C26-C27-C28</f>
+        <v>49.540000000000006</v>
+      </c>
+      <c r="D29" s="53"/>
+      <c r="E29" s="53"/>
+      <c r="F29" s="53"/>
+      <c r="G29" s="53"/>
+      <c r="H29" s="53"/>
+      <c r="I29" s="53"/>
+      <c r="J29" s="53"/>
+    </row>
+    <row r="30" spans="1:10" s="31" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="30"/>
+      <c r="B30" s="61"/>
+      <c r="C30" s="44"/>
+      <c r="D30" s="44"/>
+      <c r="E30" s="44"/>
+      <c r="F30" s="44"/>
+      <c r="G30" s="44"/>
+      <c r="H30" s="44"/>
+      <c r="I30" s="44"/>
+      <c r="J30" s="44"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="32.1640625" style="14" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" style="18" customWidth="1"/>
+    <col min="3" max="16384" width="8.83203125" style="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="29" customFormat="1" ht="21" x14ac:dyDescent="0.25">
+      <c r="A1" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="R1" s="30" t="s">
+      <c r="B1" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="S1" s="30" t="s">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="16">
+        <f>SUM(Event_PnL!B11:'Event_PnL'!Z11)</f>
+        <v>80365.819999999992</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="16">
+        <f>B2-B8</f>
+        <v>73814.759999999995</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4" s="18">
+        <f>SUM((Event_PnL!B18:'Event_PnL'!Z18):(Event_PnL!B19:'Event_PnL'!Z19))</f>
+        <v>10725.349999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="B5" s="17">
+        <f>B4/B3</f>
+        <v>0.14530088562233351</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
-        <v>46081</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" s="3">
-        <v>133</v>
-      </c>
-      <c r="E2" s="6">
-        <v>550</v>
-      </c>
-      <c r="F2" s="7">
-        <v>7572.1</v>
-      </c>
-      <c r="G2" s="7">
-        <v>0</v>
-      </c>
-      <c r="H2" s="6">
-        <v>10000</v>
-      </c>
-      <c r="I2" s="6">
-        <v>16320</v>
-      </c>
-      <c r="J2" s="6">
-        <v>29967</v>
-      </c>
-      <c r="K2" s="6">
-        <v>13072.51</v>
-      </c>
-      <c r="L2" s="6">
-        <v>6204.47</v>
-      </c>
-      <c r="M2" s="6">
-        <v>76113.98</v>
-      </c>
-      <c r="N2" s="6">
-        <f xml:space="preserve"> SUM(H2, I2,J2,K2)</f>
-        <v>69359.509999999995</v>
-      </c>
-      <c r="O2" s="6">
-        <f>N2 - F2 -I2-J2-E2</f>
-        <v>14950.409999999996</v>
-      </c>
-      <c r="P2" s="8">
-        <f>(O2 / N2)</f>
-        <v>0.21554953314981604</v>
-      </c>
-      <c r="Q2" s="9">
-        <f>N2 / D2</f>
-        <v>521.50007518796986</v>
-      </c>
-      <c r="R2" s="9">
-        <f>J2/D2</f>
-        <v>225.31578947368422</v>
-      </c>
-      <c r="S2" s="9">
-        <f>F2/D2</f>
-        <v>56.933082706766918</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
-        <v>46082</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" s="3">
-        <v>30</v>
-      </c>
-      <c r="E3" s="3">
-        <v>0</v>
-      </c>
-      <c r="F3" s="7">
-        <v>1269.7</v>
-      </c>
-      <c r="G3" s="7">
-        <v>0</v>
-      </c>
-      <c r="H3" s="7">
-        <v>0</v>
-      </c>
-      <c r="I3" s="6">
-        <v>2475</v>
-      </c>
-      <c r="J3" s="5">
-        <v>700</v>
-      </c>
-      <c r="K3" s="5">
-        <v>730.25</v>
-      </c>
-      <c r="L3" s="5">
-        <v>346.59</v>
-      </c>
-      <c r="M3" s="6">
-        <v>4251.84</v>
-      </c>
-      <c r="N3" s="7">
-        <f xml:space="preserve"> SUM(H3, I3,J3,K3)</f>
-        <v>3905.25</v>
-      </c>
-      <c r="O3" s="6">
-        <f>N3 - F3 -I3-J3-E3</f>
-        <v>-539.44999999999982</v>
-      </c>
-      <c r="P3" s="8">
-        <f>(O3 / N3)</f>
-        <v>-0.13813456244798664</v>
-      </c>
-      <c r="Q3" s="9">
-        <f>N3 / D3</f>
-        <v>130.17500000000001</v>
-      </c>
-      <c r="R3" s="9">
-        <f>J3/D3</f>
-        <v>23.333333333333332</v>
-      </c>
-      <c r="S3" s="9">
-        <f>F3/D3</f>
-        <v>42.323333333333338</v>
+      <c r="B6" s="18" t="e">
+        <f>SUM(Event_PnL!#REF!:Event_PnL!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="19" t="e">
+        <f>B6/B3</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="18">
+        <f>SUM(Event_PnL!B10:'Event_PnL'!Z10)</f>
+        <v>6551.06</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="18" t="e">
+        <f>SUM(B4,B6)</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" s="18">
+        <f>SUM(Event_PnL!B23:'Event_PnL'!Z23)</f>
+        <v>44305.81</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" s="19" t="e">
+        <f>B9/B3</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" s="19">
+        <f>(B10/B3)</f>
+        <v>0.60022968306067781</v>
       </c>
     </row>
   </sheetData>
@@ -1510,55 +1908,55 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="19" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="21" style="13" customWidth="1"/>
-    <col min="2" max="2" width="53.1640625" style="13" customWidth="1"/>
-    <col min="3" max="3" width="15" style="16" customWidth="1"/>
-    <col min="4" max="4" width="7.1640625" style="13" customWidth="1"/>
-    <col min="5" max="5" width="22.6640625" style="17" customWidth="1"/>
-    <col min="6" max="16384" width="8.83203125" style="13"/>
+    <col min="1" max="1" width="21" style="7" customWidth="1"/>
+    <col min="2" max="2" width="53.1640625" style="7" customWidth="1"/>
+    <col min="3" max="3" width="15" style="10" customWidth="1"/>
+    <col min="4" max="4" width="7.1640625" style="7" customWidth="1"/>
+    <col min="5" max="5" width="22.6640625" style="11" customWidth="1"/>
+    <col min="6" max="16384" width="8.83203125" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="36" customFormat="1" ht="21" x14ac:dyDescent="0.2">
-      <c r="A1" s="34" t="s">
+    <row r="1" spans="1:5" s="24" customFormat="1" ht="21" x14ac:dyDescent="0.2">
+      <c r="A1" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="34" t="s">
+      <c r="B1" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="E1" s="37" t="s">
-        <v>34</v>
+      <c r="C1" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="25" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="14">
+      <c r="A2" s="8">
         <v>46081</v>
       </c>
-      <c r="B2" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" s="16">
+      <c r="B2" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="10">
         <v>7627.1</v>
       </c>
-      <c r="E2" s="17">
+      <c r="E2" s="11">
         <v>11880.8</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="14">
+      <c r="A3" s="8">
         <v>46082</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C3" s="16">
+      <c r="B3" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="10">
         <v>1269.7</v>
       </c>
     </row>
@@ -1568,7 +1966,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
@@ -1579,331 +1977,205 @@
     <col min="4" max="4" width="40.33203125" style="1" customWidth="1"/>
     <col min="5" max="5" width="14" style="2" customWidth="1"/>
     <col min="6" max="6" width="53" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.6640625" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.83203125" style="1"/>
+    <col min="7" max="8" width="13.6640625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="38" customFormat="1" ht="21" x14ac:dyDescent="0.2">
-      <c r="A1" s="32" t="s">
+    <row r="1" spans="1:7" s="26" customFormat="1" ht="21" x14ac:dyDescent="0.2">
+      <c r="A1" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="C1" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="32" t="s">
+      <c r="D1" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="32" t="s">
+      <c r="E1" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="F1" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="32" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="11">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="5">
         <v>46078</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="6">
+        <v>111</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="6">
+        <f>SUM(E2:E10)</f>
+        <v>6311.9999999999991</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="5">
+        <v>46079</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="6">
+        <v>371.83</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" s="4"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
+        <v>46077</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="6">
+        <v>3388.2</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G4" s="4"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="5">
+        <v>46078</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10" t="s">
+      <c r="E5" s="6">
+        <v>377.52</v>
+      </c>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="5"/>
+      <c r="B6" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E2" s="12">
-        <v>111</v>
-      </c>
-      <c r="F2" s="10" t="s">
+      <c r="C6" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="G2" s="12">
-        <f>SUM(E2:E10)</f>
-        <v>6697.9099999999989</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11">
-        <v>46079</v>
-      </c>
-      <c r="B3" s="10" t="s">
+      <c r="D6" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="13">
+        <v>559.5</v>
+      </c>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="5"/>
+      <c r="B7" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10" t="s">
+      <c r="D7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="6">
+        <v>415.28</v>
+      </c>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="E3" s="12">
-        <v>399.2</v>
-      </c>
-      <c r="F3" s="10" t="s">
+      <c r="C8" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G3" s="10"/>
-    </row>
-    <row r="4" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11">
-        <v>46077</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="E4" s="12">
-        <v>3992</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="G4" s="10"/>
-    </row>
-    <row r="5" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="11">
-        <v>46078</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="E5" s="12">
-        <v>377.52</v>
-      </c>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-    </row>
-    <row r="6" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="11"/>
-      <c r="B6" s="10" t="s">
+      <c r="D8" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="6">
+        <v>135.72</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G8" s="4"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C9" s="4"/>
+      <c r="D9" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D6" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="E6" s="19">
-        <v>559.5</v>
-      </c>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-    </row>
-    <row r="7" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="11"/>
-      <c r="B7" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="E7" s="12">
-        <v>415.28</v>
-      </c>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-    </row>
-    <row r="8" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10"/>
-      <c r="B8" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="E8" s="12">
-        <v>135.72</v>
-      </c>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-    </row>
-    <row r="9" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="10"/>
-      <c r="B9" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10" t="s">
+      <c r="E9" s="6">
+        <v>145.19999999999999</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G9" s="4"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E9" s="12">
-        <v>145.19999999999999</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="G9" s="10"/>
-    </row>
-    <row r="10" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="10"/>
-      <c r="B10" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="E10" s="12">
-        <v>562.49</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="G10" s="10"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" s="6">
+        <v>807.75</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="24" style="20" customWidth="1"/>
-    <col min="2" max="2" width="19.33203125" style="24" customWidth="1"/>
-    <col min="3" max="16384" width="8.83203125" style="20"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" s="41" customFormat="1" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="39" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" s="40" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="B2" s="22">
-        <v>80365.820000000007</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="B3" s="22">
-        <f>B2-B8</f>
-        <v>73814.760000000009</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="B4" s="23">
-        <f>B5/B3</f>
-        <v>9.0739440187843176E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="24">
-        <v>6697.91</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="B6" s="25">
-        <f>B7/B3</f>
-        <v>0.16095425901269608</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="24">
-        <v>11880.8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="B8" s="24">
-        <v>6551.06</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="B9" s="24">
-        <f>SUM(B5,B7)</f>
-        <v>18578.71</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="B10" s="24">
-        <f xml:space="preserve"> B3-B5-B7</f>
-        <v>55236.05</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="B11" s="25">
-        <f>B10/B3</f>
-        <v>0.7483063007994607</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="B12" s="25">
-        <f>B9/B3</f>
-        <v>0.25169369920053924</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="B13" s="25">
-        <f>(B10/B3)</f>
-        <v>0.7483063007994607</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C27D3B0-A098-8248-9A91-D0FDD0C1B522}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
